--- a/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Dounia est dans l'entrée. Le sac est par terre. Il est rouge. Maman est là, près de Dounia. Maman est l'adulte. Maman dit : la gourde, le chapeau, le goûter. Dounia écoute. Dounia voit la gourde verte. Elle la prend. Elle la met dans le sac. Dounia voit le chapeau souple. Elle le prend. Elle le met dans le sac. Dounia voit le petit goûter. Elle le prend. Elle le met dans le sac. Dounia appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Dounia a mis ce que l'adulte a dit. Maman pose la main sur le sac. Maman dit : merci Dounia. Le sac est prêt.</t>
+          <t>C'est le matin. Dounia est dans l'entrée. Le sac est par terre. Il est rouge. Maman est là, près de Dounia. Maman est l'adulte. La gourde, le chapeau, le goûter. Dounia écoute. Dounia voit la gourde verte. Elle la prend. Elle la met dans le sac. Dounia voit le chapeau souple. Elle le prend. Elle le met dans le sac. Dounia voit le petit goûter. Elle le prend. Elle le met dans le sac. Dounia appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Dounia a mis ce que l'adulte a dit. Maman pose la main sur le sac. Merci Dounia. Le sac est prêt.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Dounia est dans l'entrée. Le sac est par terre. Il est rouge. Maman est là, près de Dounia. Maman est l'adulte.
+maman|La gourde, le chapeau, le goûter.
+narrateur|Dounia écoute. Dounia voit la gourde verte. Elle la prend. Elle la met dans le sac. Dounia voit le chapeau souple. Elle le prend. Elle le met dans le sac. Dounia voit le petit goûter. Elle le prend. Elle le met dans le sac. Dounia appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Dounia a mis ce que l'adulte a dit. Maman pose la main sur le sac.
+maman|Merci Dounia.
+narrateur|Le sac est prêt.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia prépare le sac. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia a écouté. Elle a mis la gourde. Elle a mis le chapeau. Elle a mis le goûter. Le sac est prêt. C'est ce que l'adulte a dit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia prend le sac. La sangle est lisse. Maman ouvre la porte. Elles partent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Le sac est prêt.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Dounia prépare le sac. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Dounia a écouté. Elle a mis la gourde. Elle a mis le chapeau. Elle a mis le goûter. Le sac est prêt. C'est ce que l'adulte a dit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Dounia prend le sac. La sangle est lisse. Maman ouvre la porte. Elles partent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dounia prépare son sac</t>
+          <t>Le sac rouge de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'odeur du biscuit glisse jusqu'à l'entrée. Nino met la gourde, le chapeau et le goûter dans le sac rouge. Maman dit merci. Elles partent.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Dounia est dans l'entrée. Le sac est par terre. Il est rouge. Maman est là, près de Dounia. Maman est l'adulte. La gourde, le chapeau, le goûter. Dounia écoute. Dounia voit la gourde verte. Elle la prend. Elle la met dans le sac. Dounia voit le chapeau souple. Elle le prend. Elle le met dans le sac. Dounia voit le petit goûter. Elle le prend. Elle le met dans le sac. Dounia appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Dounia a mis ce que l'adulte a dit. Maman pose la main sur le sac. Merci Dounia. Le sac est prêt.</t>
+          <t>Ça sent le biscuit tout chaud. L'odeur vient de la cuisine. Elle glisse jusqu'à l'entrée. Les crochets tiennent les manteaux. Un tapis gris est un peu rêche. Dehors, une feuille bouge. Nino, viens près du sac. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse. Il est rouge, maman. Oui. C'est ton sac. On met ce que l'adulte a dit. La gourde, le chapeau, le goûter. La gourde, le chapeau, le goûter. Nino écoute. Il voit la gourde verte. Elle est un peu froide. Tu la mets dans le sac ? Nino prend la gourde. Il la met dans le sac. Bravo. La gourde est dedans. Nino voit le chapeau souple. Il est sur le crochet. Il est tout mou. Tu le mets dans le sac ? Nino prend le chapeau. Il le met dans le sac. Bravo. Le chapeau est dedans. Nino voit le petit goûter. Le papier fait un bruit doux. Ça sent encore le biscuit. Tu mets le goûter aussi ? Nino prend le goûter. Il le met dans le sac. Tu as mis ce que l'adulte a dit. Nino appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Merci Nino. Le sac est prêt ? Oui, maman. Bravo. Tu as fait du bon travail. L'odeur du biscuit reste un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Dounia est dans l'entrée. Le sac est par terre. Il est rouge. Maman est là, près de Dounia. Maman est l'adulte.
+          <t>narrateur|Ça sent le biscuit tout chaud.
+narrateur|L'odeur vient de la cuisine.
+narrateur|Elle glisse jusqu'à l'entrée.
+narrateur|Les crochets tiennent les manteaux.
+narrateur|Un tapis gris est un peu rêche.
+narrateur|Dehors, une feuille bouge.
+maman|Nino, viens près du sac.
+narrateur|En ce moment, Nino s'accroupit.
+narrateur|Le sac rouge est par terre.
+narrateur|La sangle est lisse.
+enfant-m|Il est rouge, maman.
+maman|Oui. C'est ton sac.
+maman|On met ce que l'adulte a dit.
 maman|La gourde, le chapeau, le goûter.
-narrateur|Dounia écoute. Dounia voit la gourde verte. Elle la prend. Elle la met dans le sac. Dounia voit le chapeau souple. Elle le prend. Elle le met dans le sac. Dounia voit le petit goûter. Elle le prend. Elle le met dans le sac. Dounia appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Dounia a mis ce que l'adulte a dit. Maman pose la main sur le sac.
-maman|Merci Dounia.
-narrateur|Le sac est prêt.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|La gourde, le chapeau, le goûter.
+narrateur|Nino écoute.
+narrateur|Il voit la gourde verte.
+narrateur|Elle est un peu froide.
+maman|Tu la mets dans le sac ?
+narrateur|Nino prend la gourde.
+narrateur|Il la met dans le sac.
+maman|Bravo. La gourde est dedans.
+narrateur|Nino voit le chapeau souple.
+narrateur|Il est sur le crochet.
+enfant-m|Il est tout mou.
+maman|Tu le mets dans le sac ?
+narrateur|Nino prend le chapeau.
+narrateur|Il le met dans le sac.
+maman|Bravo. Le chapeau est dedans.
+narrateur|Nino voit le petit goûter.
+narrateur|Le papier fait un bruit doux.
+narrateur|Ça sent encore le biscuit.
+maman|Tu mets le goûter aussi ?
+narrateur|Nino prend le goûter.
+narrateur|Il le met dans le sac.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|Nino appuie sur la fermeture.
+narrateur|Ça fait zzz.
+narrateur|Le sac est fermé.
+maman|Merci Nino.
+maman|Le sac est prêt ?
+enfant-m|Oui, maman.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|L'odeur du biscuit reste un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1394,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Dounia prépare le sac. Que fait-elle ?</t>
+          <t>Nino prépare le sac. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1554,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Dounia prépare le sac. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino prépare le sac.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1582,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dounia a écouté. Elle a mis la gourde. Elle a mis le chapeau. Elle a mis le goûter. Le sac est prêt. C'est ce que l'adulte a dit.</t>
+          <t>Nino a écouté. Il a mis la gourde. Il a mis le chapeau. Il a mis le goûter. Le sac est prêt. C'est ce que l'adulte a dit. Tu as fini de préparer le sac ? Oui. Bravo. Le sac est prêt. Nino pose la main sur le sac. Le rouge est un peu vif. Le papier du goûter ne fait plus de bruit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1726,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dounia a écouté. Elle a mis la gourde. Elle a mis le chapeau. Elle a mis le goûter. Le sac est prêt. C'est ce que l'adulte a dit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino a écouté.
+narrateur|Il a mis la gourde.
+narrateur|Il a mis le chapeau.
+narrateur|Il a mis le goûter.
+narrateur|Le sac est prêt.
+narrateur|C'est ce que l'adulte a dit.
+maman|Tu as fini de préparer le sac ?
+enfant-m|Oui.
+maman|Bravo. Le sac est prêt.
+narrateur|Nino pose la main sur le sac.
+narrateur|Le rouge est un peu vif.
+narrateur|Le papier du goûter ne fait plus de bruit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1764,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dounia prend le sac. La sangle est lisse. Maman ouvre la porte. Elles partent.</t>
+          <t>Nino prend le sac. La sangle est lisse. On met tes chaussures ? Nino enfile ses chaussures. Tu as fini tes chaussures ? Oui, maman. Bravo. Maman ouvre la porte. L'air sent encore le biscuit. Ils partent. Le sac rouge tape doucement.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1904,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Dounia prend le sac. La sangle est lisse. Maman ouvre la porte. Elles partent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino prend le sac.
+narrateur|La sangle est lisse.
+maman|On met tes chaussures ?
+narrateur|Nino enfile ses chaussures.
+maman|Tu as fini tes chaussures ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Maman ouvre la porte.
+narrateur|L'air sent encore le biscuit.
+narrateur|Ils partent.
+narrateur|Le sac rouge tape doucement.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1941,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le goûter voyage dans le sac. La gourde et le chapeau aussi. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Bravo, Nino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2081,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le goûter voyage dans le sac.
+narrateur|La gourde et le chapeau aussi.
+enfant-m|Le sac est prêt.
+maman|Oui. Tu as mis ce que l'adulte a dit.
+maman|Bravo, Nino.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le sac rouge de Nino</t>
+          <t>Le biscuit de Nino</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée de la maison</t>
+          <t>cuisine, entrée, jardin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dounia, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21">
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>L'odeur du biscuit glisse jusqu'à l'entrée. Nino met la gourde, le chapeau et le goûter dans le sac rouge. Maman dit merci. Elles partent.</t>
+          <t>Nino veut pique-niquer le biscuit chaud dans le jardin. Maman dit gourde, chapeau, goûter. Nino veut croquer tout de suite. Le chapeau est trop haut. Il met ce que maman a dit. Ils croquent dans l'herbe.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ça sent le biscuit tout chaud. L'odeur vient de la cuisine. Elle glisse jusqu'à l'entrée. Les crochets tiennent les manteaux. Un tapis gris est un peu rêche. Dehors, une feuille bouge. Nino, viens près du sac. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse. Il est rouge, maman. Oui. C'est ton sac. On met ce que l'adulte a dit. La gourde, le chapeau, le goûter. La gourde, le chapeau, le goûter. Nino écoute. Il voit la gourde verte. Elle est un peu froide. Tu la mets dans le sac ? Nino prend la gourde. Il la met dans le sac. Bravo. La gourde est dedans. Nino voit le chapeau souple. Il est sur le crochet. Il est tout mou. Tu le mets dans le sac ? Nino prend le chapeau. Il le met dans le sac. Bravo. Le chapeau est dedans. Nino voit le petit goûter. Le papier fait un bruit doux. Ça sent encore le biscuit. Tu mets le goûter aussi ? Nino prend le goûter. Il le met dans le sac. Tu as mis ce que l'adulte a dit. Nino appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Merci Nino. Le sac est prêt ? Oui, maman. Bravo. Tu as fait du bon travail. L'odeur du biscuit reste un peu.</t>
+          <t>La casserole fait un petit chuchotis. Ça sent le biscuit tout chaud. L'odeur glisse jusqu'à l'entrée. Une vapeur légère danse. Les crochets tiennent les manteaux. Un tapis gris est un peu rêche. Dehors, une feuille bouge. Nino, le biscuit est prêt. On le mange dehors ? Oui. On fait un pique-nique. D'abord, on prépare le sac. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse. Il est rouge, maman. Oui. C'est ton sac. On met ce que l'adulte a dit. La gourde, le chapeau, le goûter. La gourde, le chapeau, le goûter. Nino voit le petit goûter. Le papier fait un bruit doux. Ça sent encore le biscuit. Je le mange maintenant ? Plus tard. Dans le jardin. D'abord, dans le sac. Nino met le goûter. Il prend la gourde verte. Elle est un peu froide. Il la met dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est le matin. Dounia est dans l'entrée. Le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt; est par terre. Il est rouge. Maman est là, près de Dounia. Maman est l'adulte. Maman dit : la gourde, le chapeau, le goûter. Dounia écoute. Dounia voit la gourde verte. Elle la prend. Elle la met dans le sac. Dounia voit le chapeau souple. Elle le prend. Elle le met dans le sac. Dounia voit le petit goûter. Elle le prend. Elle le met dans le sac. Dounia appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Dounia a mis ce que l'adulte a dit. Maman pose la main sur le sac. Maman dit : merci Dounia. Le sac est prêt.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La casserole fait un petit chuchotis. Ça sent le biscuit tout chaud. L'odeur glisse jusqu'à l'entrée. Une vapeur légère danse. Les crochets tiennent les manteaux. Un tapis gris est un peu rêche. Dehors, une feuille bouge. Nino, le biscuit est prêt. On le mange dehors ? Oui. On fait un pique-nique. D'abord, on prépare le sac. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse. Il est rouge, maman. Oui. C'est ton sac. On met ce que l'adulte a dit. La gourde, le chapeau, le goûter. La gourde, le chapeau, le goûter. Nino voit le petit goûter. Le papier fait un bruit doux. Ça sent encore le biscuit. Je le mange maintenant ? Plus tard. Dans le jardin. D'abord, dans le sac. Nino met le goûter. Il prend la gourde verte. Elle est un peu froide. Il la met dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,13 +1324,17 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ça sent le biscuit tout chaud.
-narrateur|L'odeur vient de la cuisine.
-narrateur|Elle glisse jusqu'à l'entrée.
+          <t>narrateur|La casserole fait un petit chuchotis.
+narrateur|Ça sent le biscuit tout chaud.
+narrateur|L'odeur glisse jusqu'à l'entrée.
+narrateur|Une vapeur légère danse.
 narrateur|Les crochets tiennent les manteaux.
 narrateur|Un tapis gris est un peu rêche.
 narrateur|Dehors, une feuille bouge.
-maman|Nino, viens près du sac.
+maman|Nino, le biscuit est prêt.
+enfant-m|On le mange dehors ?
+maman|Oui. On fait un pique-nique.
+maman|D'abord, on prépare le sac.
 narrateur|En ce moment, Nino s'accroupit.
 narrateur|Le sac rouge est par terre.
 narrateur|La sangle est lisse.
@@ -1339,35 +1343,19 @@
 maman|On met ce que l'adulte a dit.
 maman|La gourde, le chapeau, le goûter.
 enfant-m|La gourde, le chapeau, le goûter.
-narrateur|Nino écoute.
-narrateur|Il voit la gourde verte.
-narrateur|Elle est un peu froide.
-maman|Tu la mets dans le sac ?
-narrateur|Nino prend la gourde.
-narrateur|Il la met dans le sac.
-maman|Bravo. La gourde est dedans.
-narrateur|Nino voit le chapeau souple.
-narrateur|Il est sur le crochet.
-enfant-m|Il est tout mou.
-maman|Tu le mets dans le sac ?
-narrateur|Nino prend le chapeau.
-narrateur|Il le met dans le sac.
-maman|Bravo. Le chapeau est dedans.
 narrateur|Nino voit le petit goûter.
 narrateur|Le papier fait un bruit doux.
 narrateur|Ça sent encore le biscuit.
-maman|Tu mets le goûter aussi ?
-narrateur|Nino prend le goûter.
-narrateur|Il le met dans le sac.
-maman|Tu as mis ce que l'adulte a dit.
-narrateur|Nino appuie sur la fermeture.
-narrateur|Ça fait zzz.
-narrateur|Le sac est fermé.
-maman|Merci Nino.
-maman|Le sac est prêt ?
-enfant-m|Oui, maman.
-maman|Bravo. Tu as fait du bon travail.
-narrateur|L'odeur du biscuit reste un peu.</t>
+enfant-m|Je le mange maintenant ?
+maman|Plus tard. Dans le jardin.
+maman|D'abord, dans le sac.
+narrateur|Nino met le goûter.
+narrateur|Il prend la gourde verte.
+narrateur|Elle est un peu froide.
+narrateur|Il la met dans le sac.
+enfant-m|Où est le chapeau ?
+narrateur|Le crochet du bas est vide.
+narrateur|Le chapeau est trop haut.</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1382,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nino prépare le sac. Que fait-il ?</t>
+          <t>Nino prépare le sac. Où met-il les affaires ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dounia prépare le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino prépare le sac. Où met-il les affaires ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1414,7 +1402,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le sac | elle met | dans le sac | mettre</t>
+          <t>le sac | dans le sac | il met | mettre | la gourde | le chapeau | le goûter</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1429,7 +1417,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle met les affaires dans le sac. Que fait Dounia ?</t>
+          <t>Il met les affaires dans le sac. Où les met-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1478,7 +1466,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1555,7 +1543,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Nino prépare le sac.
-narrateur|Que fait-il ?</t>
+narrateur|Où met-il les affaires ?</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1570,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a écouté. Il a mis la gourde. Il a mis le chapeau. Il a mis le goûter. Le sac est prêt. C'est ce que l'adulte a dit. Tu as fini de préparer le sac ? Oui. Bravo. Le sac est prêt. Nino pose la main sur le sac. Le rouge est un peu vif. Le papier du goûter ne fait plus de bruit.</t>
+          <t>Je te le donne. Maman tend le chapeau. Il est tout mou. Nino le met dans le sac. Tu as mis ce que l'adulte a dit. Nino appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le sac. Le rouge est un peu vif. Le papier du goûter se tait. Le biscuit voyage avec nous. Dans le sac.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dounia a écouté. Elle a mis la gourde. Elle a mis le chapeau. Elle a mis le goûter. Le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt; est prêt. C'est ce que l'adulte a dit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je te le donne. Maman tend le chapeau. Il est tout mou. Nino le met dans le sac. Tu as mis ce que l'adulte a dit. Nino appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le sac. Le rouge est un peu vif. Le papier du goûter se tait. Le biscuit voyage avec nous. Dans le sac.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1650,7 +1638,7 @@
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1726,18 +1714,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino a écouté.
-narrateur|Il a mis la gourde.
-narrateur|Il a mis le chapeau.
-narrateur|Il a mis le goûter.
-narrateur|Le sac est prêt.
-narrateur|C'est ce que l'adulte a dit.
-maman|Tu as fini de préparer le sac ?
-enfant-m|Oui.
-maman|Bravo. Le sac est prêt.
+          <t>maman|Je te le donne.
+narrateur|Maman tend le chapeau.
+narrateur|Il est tout mou.
+narrateur|Nino le met dans le sac.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|Nino appuie sur la fermeture.
+narrateur|Ça fait zzz.
+narrateur|Le sac est fermé.
+maman|Le sac est prêt ?
+enfant-m|Oui, maman.
 narrateur|Nino pose la main sur le sac.
 narrateur|Le rouge est un peu vif.
-narrateur|Le papier du goûter ne fait plus de bruit.</t>
+narrateur|Le papier du goûter se tait.
+maman|Le biscuit voyage avec nous.
+enfant-m|Dans le sac.</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1755,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino prend le sac. La sangle est lisse. On met tes chaussures ? Nino enfile ses chaussures. Tu as fini tes chaussures ? Oui, maman. Bravo. Maman ouvre la porte. L'air sent encore le biscuit. Ils partent. Le sac rouge tape doucement.</t>
+          <t>On met tes chaussures. Nino enfile ses chaussures. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air sent encore le biscuit. L'herbe est un peu fraîche. Ils s'assoient près de la feuille. Le goûter, maintenant ? Oui. Il est dans le sac. Nino ouvre un tout petit peu. Le papier fait encore un bruit. Une fourmi passe dans l'herbe. Elle veut le biscuit ? Elle a son chemin. Nous, le nôtre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dounia prend le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. La sangle est lisse. Maman ouvre la porte. Elles partent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On met tes chaussures. Nino enfile ses chaussures. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air sent encore le biscuit. L'herbe est un peu fraîche. Ils s'assoient près de la feuille. Le goûter, maintenant ? Oui. Il est dans le sac. Nino ouvre un tout petit peu. Le papier fait encore un bruit. Une fourmi passe dans l'herbe. Elle veut le biscuit ? Elle a son chemin. Nous, le nôtre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1832,7 +1823,7 @@
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1904,17 +1895,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nino prend le sac.
-narrateur|La sangle est lisse.
-maman|On met tes chaussures ?
+          <t>maman|On met tes chaussures.
 narrateur|Nino enfile ses chaussures.
 maman|Tu as fini tes chaussures ?
 enfant-m|Oui, maman.
-maman|Bravo.
 narrateur|Maman ouvre la porte.
 narrateur|L'air sent encore le biscuit.
-narrateur|Ils partent.
-narrateur|Le sac rouge tape doucement.</t>
+narrateur|L'herbe est un peu fraîche.
+narrateur|Ils s'assoient près de la feuille.
+enfant-m|Le goûter, maintenant ?
+maman|Oui. Il est dans le sac.
+narrateur|Nino ouvre un tout petit peu.
+narrateur|Le papier fait encore un bruit.
+narrateur|Une fourmi passe dans l'herbe.
+enfant-m|Elle veut le biscuit ?
+maman|Elle a son chemin.
+maman|Nous, le nôtre.</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le goûter voyage dans le sac. La gourde et le chapeau aussi. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Bravo, Nino. L'histoire est finie.</t>
+          <t>Nino croque le biscuit. Il est encore un peu chaud. Le sac rouge repose dans l'herbe. Le sac était prêt. Oui. Tu as mis ce que l'adulte a dit. La casserole ne chuchote plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino croque le biscuit. Il est encore un peu chaud. Le sac rouge repose dans l'herbe. Le sac était prêt. Oui. Tu as mis ce que l'adulte a dit. La casserole ne chuchote plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2009,7 +2005,7 @@
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2081,11 +2077,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le goûter voyage dans le sac.
-narrateur|La gourde et le chapeau aussi.
-enfant-m|Le sac est prêt.
+          <t>narrateur|Nino croque le biscuit.
+narrateur|Il est encore un peu chaud.
+narrateur|Le sac rouge repose dans l'herbe.
+enfant-m|Le sac était prêt.
 maman|Oui. Tu as mis ce que l'adulte a dit.
-maman|Bravo, Nino.
+narrateur|La casserole ne chuchote plus.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2107,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2152,6 +2149,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le biscuit de Nino</t>
+          <t>Le pique-nique de la pente</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nino veut pique-niquer le biscuit chaud dans le jardin. Maman dit gourde, chapeau, goûter. Nino veut croquer tout de suite. Le chapeau est trop haut. Il met ce que maman a dit. Ils croquent dans l'herbe.</t>
+          <t>Nino veut pique-niquer le biscuit sur la pente. La gourde pique, le chapeau est trop haut. Il enveloppe, range, croque dans l'herbe.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La casserole fait un petit chuchotis. Ça sent le biscuit tout chaud. L'odeur glisse jusqu'à l'entrée. Une vapeur légère danse. Les crochets tiennent les manteaux. Un tapis gris est un peu rêche. Dehors, une feuille bouge. Nino, le biscuit est prêt. On le mange dehors ? Oui. On fait un pique-nique. D'abord, on prépare le sac. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse. Il est rouge, maman. Oui. C'est ton sac. On met ce que l'adulte a dit. La gourde, le chapeau, le goûter. La gourde, le chapeau, le goûter. Nino voit le petit goûter. Le papier fait un bruit doux. Ça sent encore le biscuit. Je le mange maintenant ? Plus tard. Dans le jardin. D'abord, dans le sac. Nino met le goûter. Il prend la gourde verte. Elle est un peu froide. Il la met dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut.</t>
+          <t>Le vent de la pente plie l'herbe. L'herbe sent le foin, tout sec. La maison de bois craque un peu. Une casserole chuchote dans la cuisine. Ça sent le biscuit tout chaud. Une vapeur légère danse près du four. Dehors, une pierre grise chauffe déjà. Un oiseau de montagne crie, tout haut. Nino, le biscuit est prêt. On le mange dehors ? Oui, sur la pente. Un pique-nique, tout petit. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse, un peu froide. Il est rouge, maman. Oui, c'est le tien. Le goûter d'abord, encore chaud. Nino prend le petit paquet. Le papier fait un bruit doux. Ça sent encore le biscuit. Je le mange maintenant ? Plus tard, dans l'herbe. D'abord, dans le sac. Nino pose le goûter dedans. Prends aussi de l'eau. Nino prend la gourde verte. Elle est trop froide pour ses doigts. Aïe, elle pique. Enveloppe-la dans le linge. Un linge à carreaux attend sur la table. Nino l'enroule autour de l'eau. Le froid s'en va un peu. C'est mieux. Il pose la gourde dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut. Je te le tends ? Oui, s'il te plaît.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La casserole fait un petit chuchotis. Ça sent le biscuit tout chaud. L'odeur glisse jusqu'à l'entrée. Une vapeur légère danse. Les crochets tiennent les manteaux. Un tapis gris est un peu rêche. Dehors, une feuille bouge. Nino, le biscuit est prêt. On le mange dehors ? Oui. On fait un pique-nique. D'abord, on prépare le sac. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse. Il est rouge, maman. Oui. C'est ton sac. On met ce que l'adulte a dit. La gourde, le chapeau, le goûter. La gourde, le chapeau, le goûter. Nino voit le petit goûter. Le papier fait un bruit doux. Ça sent encore le biscuit. Je le mange maintenant ? Plus tard. Dans le jardin. D'abord, dans le sac. Nino met le goûter. Il prend la gourde verte. Elle est un peu froide. Il la met dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut.</t>
+          <t>Le vent de la pente plie l'herbe. L'herbe sent le foin, tout sec. La maison de bois craque un peu. Une casserole chuchote dans la cuisine. Ça sent le biscuit tout chaud. Une vapeur légère danse près du four. Dehors, une pierre grise chauffe déjà. Un oiseau de montagne crie, tout haut. Nino, le biscuit est prêt. On le mange dehors ? Oui, sur la pente. Un pique-nique, tout petit. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse, un peu froide. Il est rouge, maman. Oui, c'est le tien. Le goûter d'abord, encore chaud. Nino prend le petit paquet. Le papier fait un bruit doux. Ça sent encore le biscuit. Je le mange maintenant ? Plus tard, dans l'herbe. D'abord, dans le sac. Nino pose le goûter dedans. Prends aussi de l'eau. Nino prend la gourde verte. Elle est trop froide pour ses doigts. Aïe, elle pique. Enveloppe-la dans le linge. Un linge à carreaux attend sur la table. Nino l'enroule autour de l'eau. Le froid s'en va un peu. C'est mieux. Il pose la gourde dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut. Je te le tends ? Oui, s'il te plaît.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
@@ -1324,38 +1324,46 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La casserole fait un petit chuchotis.
+          <t>narrateur|Le vent de la pente plie l'herbe.
+narrateur|L'herbe sent le foin, tout sec.
+narrateur|La maison de bois craque un peu.
+narrateur|Une casserole chuchote dans la cuisine.
 narrateur|Ça sent le biscuit tout chaud.
-narrateur|L'odeur glisse jusqu'à l'entrée.
-narrateur|Une vapeur légère danse.
-narrateur|Les crochets tiennent les manteaux.
-narrateur|Un tapis gris est un peu rêche.
-narrateur|Dehors, une feuille bouge.
+narrateur|Une vapeur légère danse près du four.
+narrateur|Dehors, une pierre grise chauffe déjà.
+narrateur|Un oiseau de montagne crie, tout haut.
 maman|Nino, le biscuit est prêt.
 enfant-m|On le mange dehors ?
-maman|Oui. On fait un pique-nique.
-maman|D'abord, on prépare le sac.
+maman|Oui, sur la pente.
+maman|Un pique-nique, tout petit.
 narrateur|En ce moment, Nino s'accroupit.
 narrateur|Le sac rouge est par terre.
-narrateur|La sangle est lisse.
+narrateur|La sangle est lisse, un peu froide.
 enfant-m|Il est rouge, maman.
-maman|Oui. C'est ton sac.
-maman|On met ce que l'adulte a dit.
-maman|La gourde, le chapeau, le goûter.
-enfant-m|La gourde, le chapeau, le goûter.
-narrateur|Nino voit le petit goûter.
+maman|Oui, c'est le tien.
+maman|Le goûter d'abord, encore chaud.
+narrateur|Nino prend le petit paquet.
 narrateur|Le papier fait un bruit doux.
 narrateur|Ça sent encore le biscuit.
 enfant-m|Je le mange maintenant ?
-maman|Plus tard. Dans le jardin.
+maman|Plus tard, dans l'herbe.
 maman|D'abord, dans le sac.
-narrateur|Nino met le goûter.
-narrateur|Il prend la gourde verte.
-narrateur|Elle est un peu froide.
-narrateur|Il la met dans le sac.
+narrateur|Nino pose le goûter dedans.
+maman|Prends aussi de l'eau.
+narrateur|Nino prend la gourde verte.
+narrateur|Elle est trop froide pour ses doigts.
+enfant-m|Aïe, elle pique.
+maman|Enveloppe-la dans le linge.
+narrateur|Un linge à carreaux attend sur la table.
+narrateur|Nino l'enroule autour de l'eau.
+narrateur|Le froid s'en va un peu.
+enfant-m|C'est mieux.
+narrateur|Il pose la gourde dans le sac.
 enfant-m|Où est le chapeau ?
 narrateur|Le crochet du bas est vide.
-narrateur|Le chapeau est trop haut.</t>
+narrateur|Le chapeau est trop haut.
+maman|Je te le tends ?
+enfant-m|Oui, s'il te plaît.</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1410,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le sac | dans le sac | il met | mettre | la gourde | le chapeau | le goûter</t>
+          <t>le sac | dans le sac | il met | elle met | mettre</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1417,7 +1425,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les affaires dans le sac. Où les met-il ?</t>
+          <t>Il met les affaires dans le sac. Où les met Nino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1570,12 +1578,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Je te le donne. Maman tend le chapeau. Il est tout mou. Nino le met dans le sac. Tu as mis ce que l'adulte a dit. Nino appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le sac. Le rouge est un peu vif. Le papier du goûter se tait. Le biscuit voyage avec nous. Dans le sac.</t>
+          <t>Maman tend le chapeau. Il est tout mou, un peu chaud. Nino le met dans le sac. Il est dedans. Merci, Nino. Tu as aidé tes doigts aussi. Nino appuie sur la fermeture. Ça fait zzz. Le sac rouge est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le rouge. Le papier du goûter se tait. Le biscuit voyage avec nous. Dans le sac. On met tes chaussures ? Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Je te le donne. Maman tend le chapeau. Il est tout mou. Nino le met dans le sac. Tu as mis ce que l'adulte a dit. Nino appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le sac. Le rouge est un peu vif. Le papier du goûter se tait. Le biscuit voyage avec nous. Dans le sac.</t>
+          <t>Maman tend le chapeau. Il est tout mou, un peu chaud. Nino le met dans le sac. Il est dedans. Merci, Nino. Tu as aidé tes doigts aussi. Nino appuie sur la fermeture. Ça fait zzz. Le sac rouge est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le rouge. Le papier du goûter se tait. Le biscuit voyage avec nous. Dans le sac. On met tes chaussures ? Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1631,7 +1639,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
@@ -1714,21 +1722,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>maman|Je te le donne.
-narrateur|Maman tend le chapeau.
-narrateur|Il est tout mou.
+          <t>narrateur|Maman tend le chapeau.
+narrateur|Il est tout mou, un peu chaud.
 narrateur|Nino le met dans le sac.
-maman|Tu as mis ce que l'adulte a dit.
+enfant-m|Il est dedans.
+maman|Merci, Nino.
+maman|Tu as aidé tes doigts aussi.
 narrateur|Nino appuie sur la fermeture.
 narrateur|Ça fait zzz.
-narrateur|Le sac est fermé.
+narrateur|Le sac rouge est fermé.
 maman|Le sac est prêt ?
 enfant-m|Oui, maman.
-narrateur|Nino pose la main sur le sac.
-narrateur|Le rouge est un peu vif.
+narrateur|Nino pose la main sur le rouge.
 narrateur|Le papier du goûter se tait.
 maman|Le biscuit voyage avec nous.
-enfant-m|Dans le sac.</t>
+enfant-m|Dans le sac.
+maman|On met tes chaussures ?
+enfant-m|Oui.</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures. Nino enfile ses chaussures. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air sent encore le biscuit. L'herbe est un peu fraîche. Ils s'assoient près de la feuille. Le goûter, maintenant ? Oui. Il est dans le sac. Nino ouvre un tout petit peu. Le papier fait encore un bruit. Une fourmi passe dans l'herbe. Elle veut le biscuit ? Elle a son chemin. Nous, le nôtre.</t>
+          <t>Nino enfile ses chaussures. La semelle gratte le bois. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air de la pente entre, frais. L'herbe est un peu sèche. Ils s'assoient près d'une pierre chaude. Le goûter, maintenant ? Oui, il est dans le sac. Nino ouvre un tout petit peu. Le papier fait encore un bruit. Une fourmi passe dans l'herbe. Elle veut le biscuit ? Elle a son chemin. Nous, le nôtre. Nino sort le paquet. Le biscuit est encore un peu chaud. Il sent bon. Tu croques ? Oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures. Nino enfile ses chaussures. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air sent encore le biscuit. L'herbe est un peu fraîche. Ils s'assoient près de la feuille. Le goûter, maintenant ? Oui. Il est dans le sac. Nino ouvre un tout petit peu. Le papier fait encore un bruit. Une fourmi passe dans l'herbe. Elle veut le biscuit ? Elle a son chemin. Nous, le nôtre.</t>
+          <t>Nino enfile ses chaussures. La semelle gratte le bois. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air de la pente entre, frais. L'herbe est un peu sèche. Ils s'assoient près d'une pierre chaude. Le goûter, maintenant ? Oui, il est dans le sac. Nino ouvre un tout petit peu. Le papier fait encore un bruit. Une fourmi passe dans l'herbe. Elle veut le biscuit ? Elle a son chemin. Nous, le nôtre. Nino sort le paquet. Le biscuit est encore un peu chaud. Il sent bon. Tu croques ? Oui.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1816,7 +1826,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
@@ -1895,22 +1905,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|On met tes chaussures.
-narrateur|Nino enfile ses chaussures.
+          <t>narrateur|Nino enfile ses chaussures.
+narrateur|La semelle gratte le bois.
 maman|Tu as fini tes chaussures ?
 enfant-m|Oui, maman.
 narrateur|Maman ouvre la porte.
-narrateur|L'air sent encore le biscuit.
-narrateur|L'herbe est un peu fraîche.
-narrateur|Ils s'assoient près de la feuille.
+narrateur|L'air de la pente entre, frais.
+narrateur|L'herbe est un peu sèche.
+narrateur|Ils s'assoient près d'une pierre chaude.
 enfant-m|Le goûter, maintenant ?
-maman|Oui. Il est dans le sac.
+maman|Oui, il est dans le sac.
 narrateur|Nino ouvre un tout petit peu.
 narrateur|Le papier fait encore un bruit.
 narrateur|Une fourmi passe dans l'herbe.
 enfant-m|Elle veut le biscuit ?
 maman|Elle a son chemin.
-maman|Nous, le nôtre.</t>
+maman|Nous, le nôtre.
+narrateur|Nino sort le paquet.
+narrateur|Le biscuit est encore un peu chaud.
+enfant-m|Il sent bon.
+maman|Tu croques ?
+enfant-m|Oui.</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nino croque le biscuit. Il est encore un peu chaud. Le sac rouge repose dans l'herbe. Le sac était prêt. Oui. Tu as mis ce que l'adulte a dit. La casserole ne chuchote plus. L'histoire est finie.</t>
+          <t>Nino croque le biscuit. La croûte casse, toute légère. Il est encore chaud. Comme le four, tout à l'heure. Le sac rouge repose dans l'herbe. Le vent de la pente passe encore. Bravo, tu as préparé le pique-nique. La pierre grise reste chaude sous la main.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Nino croque le biscuit. Il est encore un peu chaud. Le sac rouge repose dans l'herbe. Le sac était prêt. Oui. Tu as mis ce que l'adulte a dit. La casserole ne chuchote plus. L'histoire est finie.</t>
+          <t>Nino croque le biscuit. La croûte casse, toute légère. Il est encore chaud. Comme le four, tout à l'heure. Le sac rouge repose dans l'herbe. Le vent de la pente passe encore. Bravo, tu as préparé le pique-nique. La pierre grise reste chaude sous la main.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1998,7 +2013,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2078,12 +2093,13 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>narrateur|Nino croque le biscuit.
-narrateur|Il est encore un peu chaud.
+narrateur|La croûte casse, toute légère.
+enfant-m|Il est encore chaud.
+maman|Comme le four, tout à l'heure.
 narrateur|Le sac rouge repose dans l'herbe.
-enfant-m|Le sac était prêt.
-maman|Oui. Tu as mis ce que l'adulte a dit.
-narrateur|La casserole ne chuchote plus.
-narrateur|L'histoire est finie.</t>
+narrateur|Le vent de la pente passe encore.
+maman|Bravo, tu as préparé le pique-nique.
+narrateur|La pierre grise reste chaude sous la main.</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2154,6 +2170,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine, entrée, jardin</t>
+          <t>chalet de montagne puis herbe de la pente</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
@@ -1952,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nino croque le biscuit. La croûte casse, toute légère. Il est encore chaud. Comme le four, tout à l'heure. Le sac rouge repose dans l'herbe. Le vent de la pente passe encore. Bravo, tu as préparé le pique-nique. La pierre grise reste chaude sous la main.</t>
+          <t>Nino croque le biscuit. La croûte casse, toute légère. Il est encore chaud. Comme le four, tout à l'heure. Le sac rouge repose dans l'herbe. Le vent de la pente passe encore. Le biscuit est encore tout chaud. La pierre grise reste chaude sous la main.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Nino croque le biscuit. La croûte casse, toute légère. Il est encore chaud. Comme le four, tout à l'heure. Le sac rouge repose dans l'herbe. Le vent de la pente passe encore. Bravo, tu as préparé le pique-nique. La pierre grise reste chaude sous la main.</t>
+          <t>Nino croque le biscuit. La croûte casse, toute légère. Il est encore chaud. Comme le four, tout à l'heure. Le sac rouge repose dans l'herbe. Le vent de la pente passe encore. Le biscuit est encore tout chaud. La pierre grise reste chaude sous la main.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
 maman|Comme le four, tout à l'heure.
 narrateur|Le sac rouge repose dans l'herbe.
 narrateur|Le vent de la pente passe encore.
-maman|Bravo, tu as préparé le pique-nique.
+maman|Le biscuit est encore tout chaud.
 narrateur|La pierre grise reste chaude sous la main.</t>
         </is>
       </c>
@@ -2120,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2177,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-03.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nino veut pique-niquer le biscuit sur la pente. La gourde pique, le chapeau est trop haut. Il enveloppe, range, croque dans l'herbe.</t>
+          <t>Nino veut croquer le biscuit chaud sur la pente, tout de suite. Il part les bras pleins : la gourde tombe. Il refuse de foncer. L'éclat de marche libère la sangle. Le sac ferme. Le biscuit croque dans l'herbe, l'éclat pâle sur le rouge.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le vent de la pente plie l'herbe. L'herbe sent le foin, tout sec. La maison de bois craque un peu. Une casserole chuchote dans la cuisine. Ça sent le biscuit tout chaud. Une vapeur légère danse près du four. Dehors, une pierre grise chauffe déjà. Un oiseau de montagne crie, tout haut. Nino, le biscuit est prêt. On le mange dehors ? Oui, sur la pente. Un pique-nique, tout petit. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse, un peu froide. Il est rouge, maman. Oui, c'est le tien. Le goûter d'abord, encore chaud. Nino prend le petit paquet. Le papier fait un bruit doux. Ça sent encore le biscuit. Je le mange maintenant ? Plus tard, dans l'herbe. D'abord, dans le sac. Nino pose le goûter dedans. Prends aussi de l'eau. Nino prend la gourde verte. Elle est trop froide pour ses doigts. Aïe, elle pique. Enveloppe-la dans le linge. Un linge à carreaux attend sur la table. Nino l'enroule autour de l'eau. Le froid s'en va un peu. C'est mieux. Il pose la gourde dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut. Je te le tends ? Oui, s'il te plaît.</t>
+          <t>Dans le chalet, une casserole chuchote. Le vent de la pente lui répond. Il glisse sous la porte, frais. Il touche la première marche. Un éclat de marche brille, pâle. Nino le voit, sans savoir. L'herbe dehors sent le foin. La maison de bois craque. Ça sent le biscuit, tout chaud. Une vapeur danse près du four. Dehors, une pierre grise chauffe. Un oiseau de montagne crie, haut. Nino, le biscuit est prêt. On le mange dehors, tout de suite ? Oui, sur la pente. Un pique-nique, tout petit. En ce moment, Nino saisit le paquet. Le papier est tiède sous les doigts. Je le porte, maman. Pas besoin du sac. Il prend aussi la gourde verte. Elle pique, trop froide. Aïe ! Il court vers la porte, les bras pleins. Le vent pousse le battant. Le paquet glisse. La gourde tombe sur le bois. Patatras. Oh. Le biscuit roule vers le seuil. Nino le rattrape, les joues chaudes. Le sourire de Nino disparaît. Dans sa poitrine, ça se bouscule. Tu voulais partir tout de suite ? Le biscuit va refroidir. Maman s'accroupit, à sa hauteur. Où le biscuit voyage-t-il mieux ? Dans mes mains. Le papier se froisse, trop lâche. Le sac rouge attend par terre. La sangle est lisse, un peu froide. Il est rouge. Oui, c'est le tien. Nino pose le biscuit dedans. Le papier se tait. L'eau aussi. Un linge à carreaux attend. Nino l'enroule autour de l'eau. C'est moins froid. Il glisse l'eau dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le vent de la pente plie l'herbe. L'herbe sent le foin, tout sec. La maison de bois craque un peu. Une casserole chuchote dans la cuisine. Ça sent le biscuit tout chaud. Une vapeur légère danse près du four. Dehors, une pierre grise chauffe déjà. Un oiseau de montagne crie, tout haut. Nino, le biscuit est prêt. On le mange dehors ? Oui, sur la pente. Un pique-nique, tout petit. En ce moment, Nino s'accroupit. Le sac rouge est par terre. La sangle est lisse, un peu froide. Il est rouge, maman. Oui, c'est le tien. Le goûter d'abord, encore chaud. Nino prend le petit paquet. Le papier fait un bruit doux. Ça sent encore le biscuit. Je le mange maintenant ? Plus tard, dans l'herbe. D'abord, dans le sac. Nino pose le goûter dedans. Prends aussi de l'eau. Nino prend la gourde verte. Elle est trop froide pour ses doigts. Aïe, elle pique. Enveloppe-la dans le linge. Un linge à carreaux attend sur la table. Nino l'enroule autour de l'eau. Le froid s'en va un peu. C'est mieux. Il pose la gourde dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut. Je te le tends ? Oui, s'il te plaît.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dans le chalet, une casserole chuchote. Le vent de la pente lui répond. Il glisse sous la porte, frais. Il touche la première marche. Un &lt;emphasis level="moderate"&gt;éclat de marche&lt;/emphasis&gt; brille, pâle. Nino le voit, sans savoir. L'herbe dehors sent le foin. La maison de bois craque. Ça sent le biscuit, tout chaud. Une vapeur danse près du four. Dehors, une pierre grise chauffe. Un oiseau de montagne crie, haut. Nino, le biscuit est prêt. On le mange dehors, tout de suite ? Oui, sur la pente. Un pique-nique, tout petit. En ce moment, Nino saisit le paquet. Le papier est tiède sous les doigts. Je le porte, maman. Pas besoin du sac. Il prend aussi la gourde verte. Elle pique, trop froide. Aïe ! Il court vers la porte, les bras pleins. Le vent pousse le battant. Le paquet glisse. La gourde tombe sur le bois. Patatras. Oh. Le biscuit roule vers le seuil. Nino le rattrape, les joues chaudes. Le sourire de Nino disparaît. Dans sa poitrine, ça se bouscule. Tu voulais partir tout de suite ? Le biscuit va refroidir. Maman s'accroupit, à sa hauteur. Où le biscuit voyage-t-il mieux ? Dans mes mains. Le papier se froisse, trop lâche. Le sac rouge attend par terre. La sangle est lisse, un peu froide. Il est rouge. Oui, c'est le tien. Nino pose le biscuit dedans. Le papier se tait. L'eau aussi. Un linge à carreaux attend. Nino l'enroule autour de l'eau. C'est moins froid. Il glisse l'eau dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;C'est le matin. Dounia est dans l'entrée. Le &lt;emphasis&gt;sac&lt;/emphasis&gt; est par terre. Il est rouge. Maman est là, près de Dounia. Maman est l'adulte. Maman dit : la gourde, le chapeau, le goûter. Dounia écoute. Dounia voit la gourde verte. Elle la prend. Elle la met dans le sac. Dounia voit le chapeau souple. Elle le prend. Elle le met dans le sac. Dounia voit le petit goûter. Elle le prend. Elle le met dans le sac. Dounia appuie sur la fermeture. Ça fait zzz. Le sac est fermé. Dounia a mis ce que l'adulte a dit. Maman pose la main sur le sac. Maman dit : merci Dounia. Le sac est prêt.&lt;/slow&gt; [pause]</t>
+          <t>Dans le chalet, une casserole chuchote. Le vent de la pente lui répond. Il glisse sous la porte, frais. Il touche la première marche. Un &lt;emphasis&gt;éclat de marche&lt;/emphasis&gt; brille, pâle. Nino le voit, sans savoir. L'herbe dehors sent le foin. La maison de bois craque. Ça sent le biscuit, tout chaud. Une vapeur danse près du four. Dehors, une pierre grise chauffe. Un oiseau de montagne crie, haut. Nino, le biscuit est prêt. On le mange dehors, tout de suite ? Oui, sur la pente. Un pique-nique, tout petit. En ce moment, Nino saisit le paquet. Le papier est tiède sous les doigts. Je le porte, maman. Pas besoin du sac. Il prend aussi la gourde verte. Elle pique, trop froide. Aïe ! Il court vers la porte, les bras pleins. Le vent pousse le battant. Le paquet glisse. La gourde tombe sur le bois. Patatras. Oh. Le biscuit roule vers le seuil. Nino le rattrape, les joues chaudes. Le sourire de Nino disparaît. Dans sa poitrine, ça se bouscule. Tu voulais partir tout de suite ? Le biscuit va refroidir. Maman s'accroupit, à sa hauteur. Où le biscuit voyage-t-il mieux ? Dans mes mains. Le papier se froisse, trop lâche. Le sac rouge attend par terre. La sangle est lisse, un peu froide. Il est rouge. Oui, c'est le tien. Nino pose le biscuit dedans. Le papier se tait. L'eau aussi. Un linge à carreaux attend. Nino l'enroule autour de l'eau. C'est moins froid. Il glisse l'eau dans le sac. Où est le chapeau ? Le crochet du bas est vide. Le chapeau est trop haut. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>éclat de marche</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1319,51 +1319,73 @@
         <v>50</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=ouvrir_le_monde; emotion=impatience; intensite=2; destinataire=enfant; sous_texte=le biscuit veut sortir tout de suite; tempo=naturel; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le vent de la pente plie l'herbe.
-narrateur|L'herbe sent le foin, tout sec.
-narrateur|La maison de bois craque un peu.
-narrateur|Une casserole chuchote dans la cuisine.
-narrateur|Ça sent le biscuit tout chaud.
-narrateur|Une vapeur légère danse près du four.
-narrateur|Dehors, une pierre grise chauffe déjà.
-narrateur|Un oiseau de montagne crie, tout haut.
+          <t>narrateur|Dans le chalet, une casserole chuchote.
+narrateur|Le vent de la pente lui répond.
+narrateur|Il glisse sous la porte, frais.
+narrateur|Il touche la première marche.
+narrateur|Un éclat de marche brille, pâle.
+narrateur|Nino le voit, sans savoir.
+narrateur|L'herbe dehors sent le foin.
+narrateur|La maison de bois craque.
+narrateur|Ça sent le biscuit, tout chaud.
+narrateur|Une vapeur danse près du four.
+narrateur|Dehors, une pierre grise chauffe.
+narrateur|Un oiseau de montagne crie, haut.
 maman|Nino, le biscuit est prêt.
-enfant-m|On le mange dehors ?
+enfant-m|On le mange dehors, tout de suite ?
 maman|Oui, sur la pente.
 maman|Un pique-nique, tout petit.
-narrateur|En ce moment, Nino s'accroupit.
-narrateur|Le sac rouge est par terre.
+narrateur|En ce moment, Nino saisit le paquet.
+narrateur|Le papier est tiède sous les doigts.
+enfant-m|Je le porte, maman.
+enfant-m|Pas besoin du sac.
+narrateur|Il prend aussi la gourde verte.
+narrateur|Elle pique, trop froide.
+enfant-m|Aïe !
+narrateur|Il court vers la porte, les bras pleins.
+narrateur|Le vent pousse le battant.
+narrateur|Le paquet glisse.
+narrateur|La gourde tombe sur le bois.
+narrateur|Patatras.
+enfant-m|Oh.
+narrateur|Le biscuit roule vers le seuil.
+narrateur|Nino le rattrape, les joues chaudes.
+narrateur|Le sourire de Nino disparaît.
+narrateur|Dans sa poitrine, ça se bouscule.
+maman|Tu voulais partir tout de suite ?
+enfant-m|Le biscuit va refroidir.
+narrateur|Maman s'accroupit, à sa hauteur.
+maman|Où le biscuit voyage-t-il mieux ?
+enfant-m|Dans mes mains.
+narrateur|Le papier se froisse, trop lâche.
+narrateur|Le sac rouge attend par terre.
 narrateur|La sangle est lisse, un peu froide.
-enfant-m|Il est rouge, maman.
+enfant-m|Il est rouge.
 maman|Oui, c'est le tien.
-maman|Le goûter d'abord, encore chaud.
-narrateur|Nino prend le petit paquet.
-narrateur|Le papier fait un bruit doux.
-narrateur|Ça sent encore le biscuit.
-enfant-m|Je le mange maintenant ?
-maman|Plus tard, dans l'herbe.
-maman|D'abord, dans le sac.
-narrateur|Nino pose le goûter dedans.
-maman|Prends aussi de l'eau.
-narrateur|Nino prend la gourde verte.
-narrateur|Elle est trop froide pour ses doigts.
-enfant-m|Aïe, elle pique.
-maman|Enveloppe-la dans le linge.
-narrateur|Un linge à carreaux attend sur la table.
+narrateur|Nino pose le biscuit dedans.
+narrateur|Le papier se tait.
+maman|L'eau aussi.
+narrateur|Un linge à carreaux attend.
 narrateur|Nino l'enroule autour de l'eau.
-narrateur|Le froid s'en va un peu.
-enfant-m|C'est mieux.
-narrateur|Il pose la gourde dans le sac.
+enfant-m|C'est moins froid.
+narrateur|Il glisse l'eau dans le sac.
 enfant-m|Où est le chapeau ?
 narrateur|Le crochet du bas est vide.
-narrateur|Le chapeau est trop haut.
-maman|Je te le tends ?
-enfant-m|Oui, s'il te plaît.</t>
+narrateur|Le chapeau est trop haut.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>vent,casserole</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1417,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nino prépare le sac. Où met-il les affaires ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nino prépare le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Où met-il les affaires ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Dounia prépare le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Que fait-elle ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nino prépare le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Où met-il les affaires ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1463,7 +1485,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1471,10 +1493,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1489,11 +1511,11 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1504,23 +1526,23 @@
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1529,13 +1551,13 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
@@ -1545,7 +1567,7 @@
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=les affaires voyagent dans le sac; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1578,17 +1600,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maman tend le chapeau. Il est tout mou, un peu chaud. Nino le met dans le sac. Il est dedans. Merci, Nino. Tu as aidé tes doigts aussi. Nino appuie sur la fermeture. Ça fait zzz. Le sac rouge est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le rouge. Le papier du goûter se tait. Le biscuit voyage avec nous. Dans le sac. On met tes chaussures ? Oui.</t>
+          <t>Nino pousse une chaise vers le crochet. La chaise glisse sur le bois. Le chapeau penche, trop loin. Je n'arrive pas. Ses épaules baissent. Tu regardes, d'abord ? Nino refuse de foncer. J'attends. Il pose un pied sur la marche. L'éclat de marche accroche la sangle. Nino tire, trop vite. La sangle reste. Ça tient. Maman se tait. Nino observe le sac, puis la marche. Le même éclat pâle, du début. C'est lui. Il soulève la sangle, sans tirer. La sangle passe. Il prend le chapeau, mou, tiède. Il le pose dans le sac. Il est dedans. Merci, Nino. La sangle est libre. Nino appuie sur la fermeture. Ça fait zzz. Le sac rouge est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le rouge. Le biscuit voyage avec nous. Dans le sac. On met tes chaussures ? Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Maman tend le chapeau. Il est tout mou, un peu chaud. Nino le met dans le sac. Il est dedans. Merci, Nino. Tu as aidé tes doigts aussi. Nino appuie sur la fermeture. Ça fait zzz. Le sac rouge est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le rouge. Le papier du goûter se tait. Le biscuit voyage avec nous. Dans le sac. On met tes chaussures ? Oui.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nino pousse une chaise vers le crochet. La chaise glisse sur le bois. Le chapeau penche, trop loin. Je n'arrive pas. Ses épaules baissent. Tu regardes, d'abord ? Nino refuse de foncer. J'attends. Il pose un pied sur la marche. L'éclat de marche accroche la &lt;emphasis level="moderate"&gt;sangle&lt;/emphasis&gt;. Nino tire, trop vite. La sangle reste. Ça tient. Maman se tait. Nino observe le sac, puis la marche. Le même éclat pâle, du début. C'est lui. Il soulève la sangle, sans tirer. La sangle passe. Il prend le chapeau, mou, tiède. Il le pose dans le sac. Il est dedans. Merci, Nino. La sangle est libre. Nino appuie sur la fermeture. Ça fait zzz. Le sac rouge est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le rouge. Le biscuit voyage avec nous. Dans le sac. On met tes chaussures ? Oui.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Dounia a écouté. Elle a mis la gourde. Elle a mis le chapeau. Elle a mis le goûter. Le &lt;emphasis&gt;sac&lt;/emphasis&gt; est prêt. C'est ce que l'adulte a dit.&lt;/slow&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nino pousse une chaise vers le crochet. La chaise glisse sur le bois. Le chapeau penche, trop loin. Je n'arrive pas. Ses épaules baissent. Tu regardes, d'abord ? Nino refuse de foncer. J'attends. Il pose un pied sur la marche. L'éclat de marche accroche la &lt;emphasis&gt;sangle&lt;/emphasis&gt;. Nino tire, trop vite. La sangle reste. Ça tient. Maman se tait. Nino observe le sac, puis la marche. Le même éclat pâle, du début. C'est lui. Il soulève la sangle, sans tirer. La sangle passe. Il prend le chapeau, mou, tiède. Il le pose dans le sac. Il est dedans. Merci, Nino. La sangle est libre. Nino appuie sur la fermeture. Ça fait zzz. Le sac rouge est fermé. Le sac est prêt ? Oui, maman. Nino pose la main sur le rouge. Le biscuit voyage avec nous. Dans le sac. On met tes chaussures ? Oui.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1635,7 +1657,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1643,22 +1665,26 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1669,30 +1695,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>sangle</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1701,46 +1727,68 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT4" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=obstacle; intention=ralentir_sans_effrayer; emotion=découragement_léger; intensite=2; destinataire=enfant; sous_texte=l_eclat de marche tient la sangle; tempo=resserré; sourire=aucun; respiration=retenue</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maman tend le chapeau.
-narrateur|Il est tout mou, un peu chaud.
-narrateur|Nino le met dans le sac.
+          <t>narrateur|Nino pousse une chaise vers le crochet.
+narrateur|La chaise glisse sur le bois.
+narrateur|Le chapeau penche, trop loin.
+enfant-m|Je n'arrive pas.
+narrateur|Ses épaules baissent.
+maman|Tu regardes, d'abord ?
+narrateur|Nino refuse de foncer.
+enfant-m|J'attends.
+narrateur|Il pose un pied sur la marche.
+narrateur|L'éclat de marche accroche la sangle.
+narrateur|Nino tire, trop vite.
+narrateur|La sangle reste.
+enfant-m|Ça tient.
+narrateur|Maman se tait.
+narrateur|Nino observe le sac, puis la marche.
+narrateur|Le même éclat pâle, du début.
+enfant-m|C'est lui.
+narrateur|Il soulève la sangle, sans tirer.
+narrateur|La sangle passe.
+narrateur|Il prend le chapeau, mou, tiède.
+narrateur|Il le pose dans le sac.
 enfant-m|Il est dedans.
 maman|Merci, Nino.
-maman|Tu as aidé tes doigts aussi.
+maman|La sangle est libre.
 narrateur|Nino appuie sur la fermeture.
 narrateur|Ça fait zzz.
 narrateur|Le sac rouge est fermé.
 maman|Le sac est prêt ?
 enfant-m|Oui, maman.
 narrateur|Nino pose la main sur le rouge.
-narrateur|Le papier du goûter se tait.
 maman|Le biscuit voyage avec nous.
 enfant-m|Dans le sac.
 maman|On met tes chaussures ?
 enfant-m|Oui.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1765,17 +1813,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino enfile ses chaussures. La semelle gratte le bois. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air de la pente entre, frais. L'herbe est un peu sèche. Ils s'assoient près d'une pierre chaude. Le goûter, maintenant ? Oui, il est dans le sac. Nino ouvre un tout petit peu. Le papier fait encore un bruit. Une fourmi passe dans l'herbe. Elle veut le biscuit ? Elle a son chemin. Nous, le nôtre. Nino sort le paquet. Le biscuit est encore un peu chaud. Il sent bon. Tu croques ? Oui.</t>
+          <t>Nino enfile ses chaussures. La semelle gratte le bois. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air de la pente entre, frais. L'herbe est un peu sèche. Ils s'assoient près d'une pierre chaude. Le goûter, maintenant ? Oui, il est dans le sac. Nino ouvre un tout petit peu. Le papier fait un bruit fin. Une fourmi passe dans l'herbe. Elle veut le biscuit ? Elle a son chemin. Nous, le nôtre. Nino sort le paquet. Le biscuit est un peu chaud. Il sent bon. Tu croques ? Oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nino enfile ses chaussures. La semelle gratte le bois. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air de la pente entre, frais. L'herbe est un peu sèche. Ils s'assoient près d'une pierre chaude. Le goûter, maintenant ? Oui, il est dans le sac. Nino ouvre un tout petit peu. Le papier fait encore un bruit. Une fourmi passe dans l'herbe. Elle veut le biscuit ? Elle a son chemin. Nous, le nôtre. Nino sort le paquet. Le biscuit est encore un peu chaud. Il sent bon. Tu croques ? Oui.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino enfile ses chaussures. La semelle gratte le bois. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air de la pente entre, frais. L'herbe est un peu sèche. Ils s'assoient près d'une pierre chaude. Le goûter, maintenant ? Oui, il est dans le sac. Nino ouvre un tout petit peu. Le papier fait un bruit fin. Une fourmi passe dans l'herbe. Elle veut le &lt;emphasis level="moderate"&gt;biscuit&lt;/emphasis&gt; ? Elle a son chemin. Nous, le nôtre. Nino sort le paquet. Le biscuit est un peu chaud. Il sent bon. Tu croques ? Oui.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Dounia prend le &lt;emphasis&gt;sac&lt;/emphasis&gt;. La sangle est lisse. Maman ouvre la porte. Elles partent.&lt;/slow&gt; [pause]</t>
+          <t>Nino enfile ses chaussures. La semelle gratte le bois. Tu as fini tes chaussures ? Oui, maman. Maman ouvre la porte. L'air de la pente entre, frais. L'herbe est un peu sèche. Ils s'assoient près d'une pierre chaude. Le goûter, maintenant ? Oui, il est dans le sac. Nino ouvre un tout petit peu. Le papier fait un bruit fin. Une fourmi passe dans l'herbe. Elle veut le &lt;emphasis&gt;biscuit&lt;/emphasis&gt; ? Elle a son chemin. Nous, le nôtre. Nino sort le paquet. Le biscuit est un peu chaud. Il sent bon. Tu croques ? Oui. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1822,7 +1870,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1830,10 +1878,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1856,30 +1904,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>biscuit</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>380</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1888,10 +1936,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1900,9 +1948,13 @@
         <v>50</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=mener_au_pique_nique; emotion=élan_retenu; intensite=2; destinataire=enfant; sous_texte=le biscuit attend dans le sac; tempo=vif; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Nino enfile ses chaussures.
@@ -1916,18 +1968,23 @@
 enfant-m|Le goûter, maintenant ?
 maman|Oui, il est dans le sac.
 narrateur|Nino ouvre un tout petit peu.
-narrateur|Le papier fait encore un bruit.
+narrateur|Le papier fait un bruit fin.
 narrateur|Une fourmi passe dans l'herbe.
 enfant-m|Elle veut le biscuit ?
 maman|Elle a son chemin.
 maman|Nous, le nôtre.
 narrateur|Nino sort le paquet.
-narrateur|Le biscuit est encore un peu chaud.
+narrateur|Le biscuit est un peu chaud.
 enfant-m|Il sent bon.
 maman|Tu croques ?
 enfant-m|Oui.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>herbe,vent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1952,17 +2009,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nino croque le biscuit. La croûte casse, toute légère. Il est encore chaud. Comme le four, tout à l'heure. Le sac rouge repose dans l'herbe. Le vent de la pente passe encore. Le biscuit est encore tout chaud. La pierre grise reste chaude sous la main.</t>
+          <t>Nino croque le biscuit. La croûte casse, toute légère. Il est chaud. Comme le four, à l'instant. Le sac rouge repose dans l'herbe. Le vent de la pente passe. La pierre grise chauffe sous la main. Sur le rouge, un éclat de marche. Il a voyagé aussi. Oui. Le même, pâle, minuscule.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Nino croque le biscuit. La croûte casse, toute légère. Il est encore chaud. Comme le four, tout à l'heure. Le sac rouge repose dans l'herbe. Le vent de la pente passe encore. Le biscuit est encore tout chaud. La pierre grise reste chaude sous la main.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino croque le biscuit. La croûte casse, toute légère. Il est chaud. Comme le four, à l'instant. Le sac rouge repose dans l'herbe. Le vent de la pente passe. La pierre grise chauffe sous la main. Sur le rouge, un &lt;emphasis level="moderate"&gt;éclat de marche&lt;/emphasis&gt;. Il a voyagé aussi. Oui. Le même, pâle, minuscule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino croque le biscuit. La croûte casse, toute légère. Il est chaud. Comme le four, à l'instant. Le sac rouge repose dans l'herbe. Le vent de la pente passe. La pierre grise chauffe sous la main. Sur le rouge, un &lt;emphasis&gt;éclat de marche&lt;/emphasis&gt;. Il a voyagé aussi. Oui. Le même, pâle, minuscule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2009,18 +2066,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2029,12 +2086,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2043,17 +2100,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de marche</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2062,11 +2123,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2075,31 +2136,38 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat de marche a voyagé sur le sac; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>narrateur|Nino croque le biscuit.
 narrateur|La croûte casse, toute légère.
-enfant-m|Il est encore chaud.
-maman|Comme le four, tout à l'heure.
+enfant-m|Il est chaud.
+maman|Comme le four, à l'instant.
 narrateur|Le sac rouge repose dans l'herbe.
-narrateur|Le vent de la pente passe encore.
-maman|Le biscuit est encore tout chaud.
-narrateur|La pierre grise reste chaude sous la main.</t>
+narrateur|Le vent de la pente passe.
+narrateur|La pierre grise chauffe sous la main.
+narrateur|Sur le rouge, un éclat de marche.
+enfant-m|Il a voyagé aussi.
+maman|Oui.
+narrateur|Le même, pâle, minuscule.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2184,6 +2252,13 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
